--- a/doc/todo-gantt-raid-v7.xlsx
+++ b/doc/todo-gantt-raid-v7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\demo-poc-ydlj\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FB2538-79F0-4CAA-8D79-C8D8D21DBF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC4D5B9-D67E-46DF-B57A-620E4AF847C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,13 +173,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -571,29 +570,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
       <c r="E2" s="4">
         <v>46300</v>
       </c>
@@ -639,36 +629,36 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="str">
-        <f>_xlfn.CONCAT(TEXT($E$2+(F2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(F2*7),"yy-mm-dd"))</f>
-        <v>26-10-05 -- 26-10-12</v>
+        <f>_xlfn.CONCAT(TEXT($E$2+(F2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(F2*7)-1,"yy-mm-dd"))</f>
+        <v>26-10-05 -- 26-10-11</v>
       </c>
       <c r="G3" s="3" t="str">
-        <f>_xlfn.CONCAT(TEXT($E$2+(G2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(G2*7),"yy-mm-dd"))</f>
-        <v>26-10-12 -- 26-10-19</v>
+        <f t="shared" ref="G3:M3" si="0">_xlfn.CONCAT(TEXT($E$2+(G2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(G2*7)-1,"yy-mm-dd"))</f>
+        <v>26-10-12 -- 26-10-18</v>
       </c>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3" si="0">_xlfn.CONCAT(TEXT($E$2+(H2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(H2*7),"yy-mm-dd"))</f>
-        <v>26-10-19 -- 26-10-26</v>
+        <f t="shared" si="0"/>
+        <v>26-10-19 -- 26-10-25</v>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3" si="1">_xlfn.CONCAT(TEXT($E$2+(I2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(I2*7),"yy-mm-dd"))</f>
-        <v>26-10-26 -- 26-11-02</v>
+        <f t="shared" si="0"/>
+        <v>26-10-26 -- 26-11-01</v>
       </c>
       <c r="J3" s="3" t="str">
-        <f t="shared" ref="J3" si="2">_xlfn.CONCAT(TEXT($E$2+(J2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(J2*7),"yy-mm-dd"))</f>
-        <v>26-11-02 -- 26-11-09</v>
+        <f t="shared" si="0"/>
+        <v>26-11-02 -- 26-11-08</v>
       </c>
       <c r="K3" s="3" t="str">
-        <f t="shared" ref="K3" si="3">_xlfn.CONCAT(TEXT($E$2+(K2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(K2*7),"yy-mm-dd"))</f>
-        <v>26-11-09 -- 26-11-16</v>
+        <f t="shared" si="0"/>
+        <v>26-11-09 -- 26-11-15</v>
       </c>
       <c r="L3" s="3" t="str">
-        <f t="shared" ref="L3" si="4">_xlfn.CONCAT(TEXT($E$2+(L2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(L2*7),"yy-mm-dd"))</f>
-        <v>26-11-16 -- 26-11-23</v>
+        <f t="shared" si="0"/>
+        <v>26-11-16 -- 26-11-22</v>
       </c>
       <c r="M3" s="3" t="str">
-        <f t="shared" ref="M3" si="5">_xlfn.CONCAT(TEXT($E$2+(M2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(M2*7),"yy-mm-dd"))</f>
-        <v>26-11-23 -- 26-11-30</v>
+        <f t="shared" si="0"/>
+        <v>26-11-23 -- 26-11-29</v>
       </c>
     </row>
   </sheetData>

--- a/doc/todo-gantt-raid-v7.xlsx
+++ b/doc/todo-gantt-raid-v7.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\demo-poc-ydlj\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC4D5B9-D67E-46DF-B57A-620E4AF847C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D25887-C0B3-488B-88C7-9FBA0094D2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="489" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TODOs" sheetId="1" r:id="rId1"/>
-    <sheet name="Gantt" sheetId="2" r:id="rId2"/>
-    <sheet name="RAID log" sheetId="3" r:id="rId3"/>
+    <sheet name="Sprint-Release-Plan" sheetId="4" r:id="rId1"/>
+    <sheet name="TODOs" sheetId="1" r:id="rId2"/>
+    <sheet name="Gantt-Chart" sheetId="2" r:id="rId3"/>
+    <sheet name="RAID-Log" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Gantt!$A$3:$M$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TODOs!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gantt-Chart'!$A$5:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TODOs!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>Status</t>
   </si>
@@ -94,6 +95,47 @@
   </si>
   <si>
     <t>Issue</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Sprint Days</t>
+  </si>
+  <si>
+    <t>Sprint Goals</t>
+  </si>
+  <si>
+    <t>Major Stories</t>
+  </si>
+  <si>
+    <t>UAT:
+DEV:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAT:
+1. xx
+2. yy
+DEV:
+1. xx
+</t>
+  </si>
+  <si>
+    <t>1. xx
+2. yy
+3. zz</t>
+  </si>
+  <si>
+    <t>Period Days</t>
+  </si>
+  <si>
+    <t>Period</t>
   </si>
 </sst>
 </file>
@@ -161,7 +203,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -169,11 +211,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -183,6 +240,33 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -462,6 +546,325 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C3464F-9D26-4B87-8005-1BDEDBB0C7C2}">
+  <dimension ref="A2:AM7"/>
+  <sheetFormatPr defaultColWidth="45.58203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="12.4140625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="14" customWidth="1"/>
+    <col min="3" max="16384" width="45.58203125" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:39">
+      <c r="A2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="13">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39">
+      <c r="A3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" s="11" customFormat="1">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="11">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11">
+        <v>2</v>
+      </c>
+      <c r="F4" s="11">
+        <v>3</v>
+      </c>
+      <c r="G4" s="11">
+        <v>4</v>
+      </c>
+      <c r="H4" s="11">
+        <v>5</v>
+      </c>
+      <c r="I4" s="11">
+        <v>6</v>
+      </c>
+      <c r="J4" s="11">
+        <v>7</v>
+      </c>
+      <c r="K4" s="11">
+        <v>8</v>
+      </c>
+      <c r="L4" s="11">
+        <v>9</v>
+      </c>
+      <c r="M4" s="11">
+        <v>10</v>
+      </c>
+      <c r="N4" s="11">
+        <v>11</v>
+      </c>
+      <c r="O4" s="11">
+        <v>12</v>
+      </c>
+      <c r="P4" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>14</v>
+      </c>
+      <c r="R4" s="11">
+        <v>15</v>
+      </c>
+      <c r="S4" s="11">
+        <v>16</v>
+      </c>
+      <c r="T4" s="11">
+        <v>17</v>
+      </c>
+      <c r="U4" s="11">
+        <v>18</v>
+      </c>
+      <c r="V4" s="11">
+        <v>19</v>
+      </c>
+      <c r="W4" s="11">
+        <v>20</v>
+      </c>
+      <c r="X4" s="11">
+        <v>21</v>
+      </c>
+      <c r="Y4" s="11">
+        <v>22</v>
+      </c>
+      <c r="Z4" s="11">
+        <v>23</v>
+      </c>
+      <c r="AA4" s="11">
+        <v>24</v>
+      </c>
+      <c r="AB4" s="11">
+        <v>25</v>
+      </c>
+      <c r="AC4" s="11">
+        <v>26</v>
+      </c>
+      <c r="AD4" s="11">
+        <v>27</v>
+      </c>
+      <c r="AE4" s="11">
+        <v>28</v>
+      </c>
+      <c r="AF4" s="11">
+        <v>29</v>
+      </c>
+      <c r="AG4" s="11">
+        <v>30</v>
+      </c>
+      <c r="AH4" s="11">
+        <v>31</v>
+      </c>
+      <c r="AI4" s="11">
+        <v>32</v>
+      </c>
+      <c r="AJ4" s="11">
+        <v>33</v>
+      </c>
+      <c r="AK4" s="11">
+        <v>34</v>
+      </c>
+      <c r="AL4" s="11">
+        <v>35</v>
+      </c>
+      <c r="AM4" s="11">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" s="11" customFormat="1">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(D4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(D4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2026-09-07 -- 2026-09-20</v>
+      </c>
+      <c r="E5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(E4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(E4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2026-09-21 -- 2026-10-04</v>
+      </c>
+      <c r="F5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(F4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(F4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2026-10-05 -- 2026-10-18</v>
+      </c>
+      <c r="G5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(G4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(G4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2026-10-19 -- 2026-11-01</v>
+      </c>
+      <c r="H5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(H4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(H4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2026-11-02 -- 2026-11-15</v>
+      </c>
+      <c r="I5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(I4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(I4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2026-11-16 -- 2026-11-29</v>
+      </c>
+      <c r="J5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(J4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(J4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2026-11-30 -- 2026-12-13</v>
+      </c>
+      <c r="K5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(K4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(K4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2026-12-14 -- 2026-12-27</v>
+      </c>
+      <c r="L5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(L4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(L4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2026-12-28 -- 2027-01-10</v>
+      </c>
+      <c r="M5" s="11" t="str">
+        <f>_xlfn.CONCAT(TEXT($B$2+(M4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(M4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-01-11 -- 2027-01-24</v>
+      </c>
+      <c r="N5" s="11" t="str">
+        <f t="shared" ref="N5:R5" si="0">_xlfn.CONCAT(TEXT($B$2+(N4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(N4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-01-25 -- 2027-02-07</v>
+      </c>
+      <c r="O5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>2027-02-08 -- 2027-02-21</v>
+      </c>
+      <c r="P5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>2027-02-22 -- 2027-03-07</v>
+      </c>
+      <c r="Q5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>2027-03-08 -- 2027-03-21</v>
+      </c>
+      <c r="R5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>2027-03-22 -- 2027-04-04</v>
+      </c>
+      <c r="S5" s="11" t="str">
+        <f t="shared" ref="S5" si="1">_xlfn.CONCAT(TEXT($B$2+(S4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(S4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-04-05 -- 2027-04-18</v>
+      </c>
+      <c r="T5" s="11" t="str">
+        <f t="shared" ref="T5" si="2">_xlfn.CONCAT(TEXT($B$2+(T4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(T4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-04-19 -- 2027-05-02</v>
+      </c>
+      <c r="U5" s="11" t="str">
+        <f t="shared" ref="U5" si="3">_xlfn.CONCAT(TEXT($B$2+(U4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(U4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-05-03 -- 2027-05-16</v>
+      </c>
+      <c r="V5" s="11" t="str">
+        <f t="shared" ref="V5:W5" si="4">_xlfn.CONCAT(TEXT($B$2+(V4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(V4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-05-17 -- 2027-05-30</v>
+      </c>
+      <c r="W5" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>2027-05-31 -- 2027-06-13</v>
+      </c>
+      <c r="X5" s="11" t="str">
+        <f t="shared" ref="X5" si="5">_xlfn.CONCAT(TEXT($B$2+(X4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(X4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-06-14 -- 2027-06-27</v>
+      </c>
+      <c r="Y5" s="11" t="str">
+        <f t="shared" ref="Y5" si="6">_xlfn.CONCAT(TEXT($B$2+(Y4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(Y4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-06-28 -- 2027-07-11</v>
+      </c>
+      <c r="Z5" s="11" t="str">
+        <f t="shared" ref="Z5" si="7">_xlfn.CONCAT(TEXT($B$2+(Z4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(Z4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-07-12 -- 2027-07-25</v>
+      </c>
+      <c r="AA5" s="11" t="str">
+        <f t="shared" ref="AA5:AB5" si="8">_xlfn.CONCAT(TEXT($B$2+(AA4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AA4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-07-26 -- 2027-08-08</v>
+      </c>
+      <c r="AB5" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v>2027-08-09 -- 2027-08-22</v>
+      </c>
+      <c r="AC5" s="11" t="str">
+        <f t="shared" ref="AC5" si="9">_xlfn.CONCAT(TEXT($B$2+(AC4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AC4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-08-23 -- 2027-09-05</v>
+      </c>
+      <c r="AD5" s="11" t="str">
+        <f t="shared" ref="AD5" si="10">_xlfn.CONCAT(TEXT($B$2+(AD4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AD4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-09-06 -- 2027-09-19</v>
+      </c>
+      <c r="AE5" s="11" t="str">
+        <f t="shared" ref="AE5" si="11">_xlfn.CONCAT(TEXT($B$2+(AE4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AE4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-09-20 -- 2027-10-03</v>
+      </c>
+      <c r="AF5" s="11" t="str">
+        <f t="shared" ref="AF5:AG5" si="12">_xlfn.CONCAT(TEXT($B$2+(AF4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AF4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-10-04 -- 2027-10-17</v>
+      </c>
+      <c r="AG5" s="11" t="str">
+        <f t="shared" si="12"/>
+        <v>2027-10-18 -- 2027-10-31</v>
+      </c>
+      <c r="AH5" s="11" t="str">
+        <f t="shared" ref="AH5" si="13">_xlfn.CONCAT(TEXT($B$2+(AH4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AH4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-11-01 -- 2027-11-14</v>
+      </c>
+      <c r="AI5" s="11" t="str">
+        <f t="shared" ref="AI5" si="14">_xlfn.CONCAT(TEXT($B$2+(AI4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AI4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-11-15 -- 2027-11-28</v>
+      </c>
+      <c r="AJ5" s="11" t="str">
+        <f t="shared" ref="AJ5" si="15">_xlfn.CONCAT(TEXT($B$2+(AJ4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AJ4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-11-29 -- 2027-12-12</v>
+      </c>
+      <c r="AK5" s="11" t="str">
+        <f t="shared" ref="AK5:AL5" si="16">_xlfn.CONCAT(TEXT($B$2+(AK4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AK4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2027-12-13 -- 2027-12-26</v>
+      </c>
+      <c r="AL5" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>2027-12-27 -- 2028-01-09</v>
+      </c>
+      <c r="AM5" s="11" t="str">
+        <f t="shared" ref="AM5" si="17">_xlfn.CONCAT(TEXT($B$2+(AM4-1)*$B$3,"yyyy-mm-dd")," -- ",TEXT($B$2+(AM4*$B$3)-1,"yyyy-mm-dd"))</f>
+        <v>2028-01-10 -- 2028-01-23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" ht="98.5" customHeight="1">
+      <c r="C6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" ht="248.5" customHeight="1">
+      <c r="C7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -555,132 +958,438 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C3AD669-CB8A-4035-87B5-3CA729AAC689}">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:BC5"/>
+  <sheetFormatPr defaultColWidth="22.58203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="17.4140625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="72.25" customWidth="1"/>
-    <col min="4" max="4" width="27.08203125" customWidth="1"/>
-    <col min="5" max="5" width="13.4140625" customWidth="1"/>
-    <col min="6" max="13" width="21.4140625" customWidth="1"/>
-    <col min="14" max="15" width="23.58203125" customWidth="1"/>
+    <col min="2" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="F1" s="5" t="s">
+    <row r="1" spans="1:55">
+      <c r="D1" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55">
+      <c r="D2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:55">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="E2" s="4">
-        <v>46300</v>
-      </c>
-      <c r="F2">
+    <row r="4" spans="1:55" s="10" customFormat="1">
+      <c r="E4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="10">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="G4" s="10">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="H4" s="10">
         <v>3</v>
       </c>
-      <c r="I2">
+      <c r="I4" s="10">
         <v>4</v>
       </c>
-      <c r="J2">
+      <c r="J4" s="10">
         <v>5</v>
       </c>
-      <c r="K2">
+      <c r="K4" s="10">
         <v>6</v>
       </c>
-      <c r="L2">
+      <c r="L4" s="10">
         <v>7</v>
       </c>
-      <c r="M2">
+      <c r="M4" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" s="2" customFormat="1">
-      <c r="A3" s="2" t="s">
+      <c r="N4" s="10">
+        <v>9</v>
+      </c>
+      <c r="O4" s="10">
+        <v>10</v>
+      </c>
+      <c r="P4" s="10">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>12</v>
+      </c>
+      <c r="R4" s="10">
+        <v>13</v>
+      </c>
+      <c r="S4" s="10">
+        <v>14</v>
+      </c>
+      <c r="T4" s="10">
+        <v>15</v>
+      </c>
+      <c r="U4" s="10">
+        <v>16</v>
+      </c>
+      <c r="V4" s="10">
+        <v>17</v>
+      </c>
+      <c r="W4" s="10">
+        <v>18</v>
+      </c>
+      <c r="X4" s="10">
+        <v>19</v>
+      </c>
+      <c r="Y4" s="10">
+        <v>20</v>
+      </c>
+      <c r="Z4" s="10">
+        <v>21</v>
+      </c>
+      <c r="AA4" s="10">
+        <v>22</v>
+      </c>
+      <c r="AB4" s="10">
+        <v>23</v>
+      </c>
+      <c r="AC4" s="10">
+        <v>24</v>
+      </c>
+      <c r="AD4" s="10">
+        <v>25</v>
+      </c>
+      <c r="AE4" s="10">
+        <v>26</v>
+      </c>
+      <c r="AF4" s="10">
+        <v>27</v>
+      </c>
+      <c r="AG4" s="10">
+        <v>28</v>
+      </c>
+      <c r="AH4" s="10">
+        <v>29</v>
+      </c>
+      <c r="AI4" s="10">
+        <v>30</v>
+      </c>
+      <c r="AJ4" s="10">
+        <v>31</v>
+      </c>
+      <c r="AK4" s="10">
+        <v>32</v>
+      </c>
+      <c r="AL4" s="10">
+        <v>33</v>
+      </c>
+      <c r="AM4" s="10">
+        <v>34</v>
+      </c>
+      <c r="AN4" s="10">
+        <v>35</v>
+      </c>
+      <c r="AO4" s="10">
+        <v>36</v>
+      </c>
+      <c r="AP4" s="10">
+        <v>37</v>
+      </c>
+      <c r="AQ4" s="10">
+        <v>38</v>
+      </c>
+      <c r="AR4" s="10">
+        <v>39</v>
+      </c>
+      <c r="AS4" s="10">
+        <v>40</v>
+      </c>
+      <c r="AT4" s="10">
+        <v>41</v>
+      </c>
+      <c r="AU4" s="10">
+        <v>42</v>
+      </c>
+      <c r="AV4" s="10">
+        <v>43</v>
+      </c>
+      <c r="AW4" s="10">
+        <v>44</v>
+      </c>
+      <c r="AX4" s="10">
+        <v>45</v>
+      </c>
+      <c r="AY4" s="10">
+        <v>46</v>
+      </c>
+      <c r="AZ4" s="10">
+        <v>47</v>
+      </c>
+      <c r="BA4" s="10">
+        <v>48</v>
+      </c>
+      <c r="BB4" s="10">
+        <v>49</v>
+      </c>
+      <c r="BC4" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:55" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="str">
-        <f>_xlfn.CONCAT(TEXT($E$2+(F2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(F2*7)-1,"yy-mm-dd"))</f>
+      <c r="F5" s="3" t="str">
+        <f>_xlfn.CONCAT(TEXT($E$1+(F4-1)*$E$2,"yy-mm-dd")," -- ",TEXT($E$1+(F4*$E$2)-1,"yy-mm-dd"))</f>
         <v>26-10-05 -- 26-10-11</v>
       </c>
-      <c r="G3" s="3" t="str">
-        <f t="shared" ref="G3:M3" si="0">_xlfn.CONCAT(TEXT($E$2+(G2-1)*7,"yy-mm-dd")," -- ",TEXT($E$2+(G2*7)-1,"yy-mm-dd"))</f>
+      <c r="G5" s="3" t="str">
+        <f t="shared" ref="G5:BC5" si="0">_xlfn.CONCAT(TEXT($E$1+(G4-1)*$E$2,"yy-mm-dd")," -- ",TEXT($E$1+(G4*$E$2)-1,"yy-mm-dd"))</f>
         <v>26-10-12 -- 26-10-18</v>
       </c>
-      <c r="H3" s="3" t="str">
+      <c r="H5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>26-10-19 -- 26-10-25</v>
       </c>
-      <c r="I3" s="3" t="str">
+      <c r="I5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>26-10-26 -- 26-11-01</v>
       </c>
-      <c r="J3" s="3" t="str">
+      <c r="J5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>26-11-02 -- 26-11-08</v>
       </c>
-      <c r="K3" s="3" t="str">
+      <c r="K5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>26-11-09 -- 26-11-15</v>
       </c>
-      <c r="L3" s="3" t="str">
+      <c r="L5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>26-11-16 -- 26-11-22</v>
       </c>
-      <c r="M3" s="3" t="str">
+      <c r="M5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>26-11-23 -- 26-11-29</v>
       </c>
+      <c r="N5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>26-11-30 -- 26-12-06</v>
+      </c>
+      <c r="O5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>26-12-07 -- 26-12-13</v>
+      </c>
+      <c r="P5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>26-12-14 -- 26-12-20</v>
+      </c>
+      <c r="Q5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>26-12-21 -- 26-12-27</v>
+      </c>
+      <c r="R5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>26-12-28 -- 27-01-03</v>
+      </c>
+      <c r="S5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-01-04 -- 27-01-10</v>
+      </c>
+      <c r="T5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-01-11 -- 27-01-17</v>
+      </c>
+      <c r="U5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-01-18 -- 27-01-24</v>
+      </c>
+      <c r="V5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-01-25 -- 27-01-31</v>
+      </c>
+      <c r="W5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-02-01 -- 27-02-07</v>
+      </c>
+      <c r="X5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-02-08 -- 27-02-14</v>
+      </c>
+      <c r="Y5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-02-15 -- 27-02-21</v>
+      </c>
+      <c r="Z5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-02-22 -- 27-02-28</v>
+      </c>
+      <c r="AA5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-03-01 -- 27-03-07</v>
+      </c>
+      <c r="AB5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-03-08 -- 27-03-14</v>
+      </c>
+      <c r="AC5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-03-15 -- 27-03-21</v>
+      </c>
+      <c r="AD5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-03-22 -- 27-03-28</v>
+      </c>
+      <c r="AE5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-03-29 -- 27-04-04</v>
+      </c>
+      <c r="AF5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-04-05 -- 27-04-11</v>
+      </c>
+      <c r="AG5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-04-12 -- 27-04-18</v>
+      </c>
+      <c r="AH5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-04-19 -- 27-04-25</v>
+      </c>
+      <c r="AI5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-04-26 -- 27-05-02</v>
+      </c>
+      <c r="AJ5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-05-03 -- 27-05-09</v>
+      </c>
+      <c r="AK5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-05-10 -- 27-05-16</v>
+      </c>
+      <c r="AL5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-05-17 -- 27-05-23</v>
+      </c>
+      <c r="AM5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-05-24 -- 27-05-30</v>
+      </c>
+      <c r="AN5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-05-31 -- 27-06-06</v>
+      </c>
+      <c r="AO5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-06-07 -- 27-06-13</v>
+      </c>
+      <c r="AP5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-06-14 -- 27-06-20</v>
+      </c>
+      <c r="AQ5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-06-21 -- 27-06-27</v>
+      </c>
+      <c r="AR5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-06-28 -- 27-07-04</v>
+      </c>
+      <c r="AS5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-07-05 -- 27-07-11</v>
+      </c>
+      <c r="AT5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-07-12 -- 27-07-18</v>
+      </c>
+      <c r="AU5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-07-19 -- 27-07-25</v>
+      </c>
+      <c r="AV5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-07-26 -- 27-08-01</v>
+      </c>
+      <c r="AW5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-08-02 -- 27-08-08</v>
+      </c>
+      <c r="AX5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-08-09 -- 27-08-15</v>
+      </c>
+      <c r="AY5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-08-16 -- 27-08-22</v>
+      </c>
+      <c r="AZ5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-08-23 -- 27-08-29</v>
+      </c>
+      <c r="BA5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-08-30 -- 27-09-05</v>
+      </c>
+      <c r="BB5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-09-06 -- 27-09-12</v>
+      </c>
+      <c r="BC5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>27-09-13 -- 27-09-19</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M3" xr:uid="{7C3AD669-CB8A-4035-87B5-3CA729AAC689}"/>
+  <autoFilter ref="A5:M5" xr:uid="{7C3AD669-CB8A-4035-87B5-3CA729AAC689}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC712FF5-733F-4668-BB91-C3058FB9B39D}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="1" max="1" width="134.25" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
